--- a/source/connector_service.xlsx
+++ b/source/connector_service.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\enterprise\omega\Папки отделов\Департамент закупівель та логістики\Відділ реінжинірингу процесів закупівель\Master data\З'єднувач\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\enterprise\omega\Папки отделов\Департамент закупівель та логістики\Відділ реінжинірингу процесів закупівель\Master data\З'єднувач\обработка\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00DD1A81-48F4-4237-91E9-B4EAC431B416}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93B275C0-E37B-4F3E-AD56-22F5686E962F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11625" xr2:uid="{CE2CFF51-9F38-4EC7-9E81-657A284ABED4}"/>
   </bookViews>
   <sheets>
     <sheet name="Аркуш1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentManualCount="10"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="976" uniqueCount="280">
   <si>
     <t>Номер карточки</t>
   </si>
@@ -605,14 +605,686 @@
     <t>_RD 97.76.42</t>
   </si>
   <si>
-    <t>Наконечник зажимной для накачки шин прямой со штуцером типа «ёлочка» 6 мм алюминиевый с стальным рычагом</t>
+    <t>алюминий</t>
+  </si>
+  <si>
+    <t>_44391150033</t>
+  </si>
+  <si>
+    <t>_RD 97.76.43</t>
+  </si>
+  <si>
+    <t>_44391150034</t>
+  </si>
+  <si>
+    <t>_RD 97.76.44</t>
+  </si>
+  <si>
+    <t>пластик</t>
+  </si>
+  <si>
+    <t>_44391150035</t>
+  </si>
+  <si>
+    <t>_RD 97.76.45</t>
+  </si>
+  <si>
+    <t>Номер группы ch3</t>
+  </si>
+  <si>
+    <t>_44141029487</t>
+  </si>
+  <si>
+    <t>_RD-0010</t>
+  </si>
+  <si>
+    <t>Пресс-маслёнка прямая с резьбой M10x1 стальная оцинкованная, комплект 10 шт.</t>
+  </si>
+  <si>
+    <t>Вид изделия: Пресс-маслёнка
+Сервисное назначение: смазка
+Каталожная роль: сервисное соединение
+Материал корпуса: сталь
+Вид покрытия: цинковое покрытие
+Количество в товарной позиции: 10 шт.
+Геометрия: прямой
+Установочное присоединение тип: резьба
+Установочное присоединение: НР M10x1
+Установочное присоединение резьба: НР M10x1
+Установочное присоединение исполнение резьбы: НР
+Установочное присоединение тип резьбы: M
+Установочное присоединение диаметр резьбы: 10
+Установочное присоединение шаг резьбы: 1.0
+Товарное наименование: Пресс-маслёнка прямая с резьбой M10x1 стальная оцинкованная, комплект 10 шт.
+Полное техническое наименование: Пресс-маслёнка прямая с резьбой M10x1 стальная оцинкованная, комплект 10 шт.</t>
+  </si>
+  <si>
+    <t>Пресс-маслёнка</t>
+  </si>
+  <si>
+    <t>смазка</t>
+  </si>
+  <si>
+    <t>НР M10x1</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>цинковое покрытие</t>
+  </si>
+  <si>
+    <t>10 шт.</t>
+  </si>
+  <si>
+    <t>_1905587012</t>
+  </si>
+  <si>
+    <t>_DK-0001</t>
+  </si>
+  <si>
+    <t>Пресс-маслёнка прямая с резьбой M10x1 стальная оцинкованная</t>
+  </si>
+  <si>
+    <t>Вид изделия: Пресс-маслёнка
+Сервисное назначение: смазка
+Каталожная роль: сервисное соединение
+Материал корпуса: сталь
+Вид покрытия: цинковое покрытие
+Количество в товарной позиции: 1 шт.
+Геометрия: прямой
+Установочное присоединение тип: резьба
+Установочное присоединение: НР M10x1
+Установочное присоединение резьба: НР M10x1
+Установочное присоединение исполнение резьбы: НР
+Установочное присоединение тип резьбы: M
+Установочное присоединение диаметр резьбы: 10
+Установочное присоединение шаг резьбы: 1.0
+Товарное наименование: Пресс-маслёнка прямая с резьбой M10x1 стальная оцинкованная
+Полное техническое наименование: Пресс-маслёнка прямая с резьбой M10x1 стальная оцинкованная</t>
+  </si>
+  <si>
+    <t>1 шт.</t>
+  </si>
+  <si>
+    <t>_44141029490</t>
+  </si>
+  <si>
+    <t>_RD-0013</t>
+  </si>
+  <si>
+    <t>Пресс-маслёнка прямая с резьбой M6x1 стальная оцинкованная, комплект 10 шт.</t>
+  </si>
+  <si>
+    <t>Вид изделия: Пресс-маслёнка
+Сервисное назначение: смазка
+Каталожная роль: сервисное соединение
+Материал корпуса: сталь
+Вид покрытия: цинковое покрытие
+Количество в товарной позиции: 10 шт.
+Геометрия: прямой
+Установочное присоединение тип: резьба
+Установочное присоединение: НР M6x1
+Установочное присоединение резьба: НР M6x1
+Установочное присоединение исполнение резьбы: НР
+Установочное присоединение тип резьбы: M
+Установочное присоединение диаметр резьбы: 6
+Установочное присоединение шаг резьбы: 1.0
+Товарное наименование: Пресс-маслёнка прямая с резьбой M6x1 стальная оцинкованная, комплект 10 шт.
+Полное техническое наименование: Пресс-маслёнка прямая с резьбой M6x1 стальная оцинкованная, комплект 10 шт.</t>
+  </si>
+  <si>
+    <t>НР M6x1</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>_1905587015</t>
+  </si>
+  <si>
+    <t>_DK-0004</t>
+  </si>
+  <si>
+    <t>Пресс-маслёнка прямая с резьбой M6x1 стальная оцинкованная</t>
+  </si>
+  <si>
+    <t>Вид изделия: Пресс-маслёнка
+Сервисное назначение: смазка
+Каталожная роль: сервисное соединение
+Материал корпуса: сталь
+Вид покрытия: цинковое покрытие
+Количество в товарной позиции: 1 шт.
+Геометрия: прямой
+Установочное присоединение тип: резьба
+Установочное присоединение: НР M6x1
+Установочное присоединение резьба: НР M6x1
+Установочное присоединение исполнение резьбы: НР
+Установочное присоединение тип резьбы: M
+Установочное присоединение диаметр резьбы: 6
+Установочное присоединение шаг резьбы: 1.0
+Товарное наименование: Пресс-маслёнка прямая с резьбой M6x1 стальная оцинкованная
+Полное техническое наименование: Пресс-маслёнка прямая с резьбой M6x1 стальная оцинкованная</t>
+  </si>
+  <si>
+    <t>_44141029493</t>
+  </si>
+  <si>
+    <t>_RD-0016</t>
+  </si>
+  <si>
+    <t>Пресс-маслёнка прямая с резьбой M8x1 стальная оцинкованная, комплект 10 шт.</t>
+  </si>
+  <si>
+    <t>Вид изделия: Пресс-маслёнка
+Сервисное назначение: смазка
+Каталожная роль: сервисное соединение
+Материал корпуса: сталь
+Вид покрытия: цинковое покрытие
+Количество в товарной позиции: 10 шт.
+Геометрия: прямой
+Установочное присоединение тип: резьба
+Установочное присоединение: НР M8x1
+Установочное присоединение резьба: НР M8x1
+Установочное присоединение исполнение резьбы: НР
+Установочное присоединение тип резьбы: M
+Установочное присоединение диаметр резьбы: 8
+Установочное присоединение шаг резьбы: 1.0
+Товарное наименование: Пресс-маслёнка прямая с резьбой M8x1 стальная оцинкованная, комплект 10 шт.
+Полное техническое наименование: Пресс-маслёнка прямая с резьбой M8x1 стальная оцинкованная, комплект 10 шт.</t>
+  </si>
+  <si>
+    <t>НР M8x1</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>_1905587018</t>
+  </si>
+  <si>
+    <t>_DK-0007</t>
+  </si>
+  <si>
+    <t>Пресс-маслёнка прямая с резьбой M8x1 стальная оцинкованная</t>
+  </si>
+  <si>
+    <t>Вид изделия: Пресс-маслёнка
+Сервисное назначение: смазка
+Каталожная роль: сервисное соединение
+Материал корпуса: сталь
+Вид покрытия: цинковое покрытие
+Количество в товарной позиции: 1 шт.
+Геометрия: прямой
+Установочное присоединение тип: резьба
+Установочное присоединение: НР M8x1
+Установочное присоединение резьба: НР M8x1
+Установочное присоединение исполнение резьбы: НР
+Установочное присоединение тип резьбы: M
+Установочное присоединение диаметр резьбы: 8
+Установочное присоединение шаг резьбы: 1.0
+Товарное наименование: Пресс-маслёнка прямая с резьбой M8x1 стальная оцинкованная
+Полное техническое наименование: Пресс-маслёнка прямая с резьбой M8x1 стальная оцинкованная</t>
+  </si>
+  <si>
+    <t>_44141029488</t>
+  </si>
+  <si>
+    <t>_RD-0011</t>
+  </si>
+  <si>
+    <t>Пресс-маслёнка угловая 45° с резьбой M10x1 стальная оцинкованная, комплект 10 шт.</t>
+  </si>
+  <si>
+    <t>Вид изделия: Пресс-маслёнка
+Сервисное назначение: смазка
+Каталожная роль: сервисное соединение
+Материал корпуса: сталь
+Вид покрытия: цинковое покрытие
+Количество в товарной позиции: 10 шт.
+Геометрия: угловой 45°
+Установочное присоединение тип: резьба
+Установочное присоединение: НР M10x1
+Установочное присоединение резьба: НР M10x1
+Установочное присоединение исполнение резьбы: НР
+Установочное присоединение тип резьбы: M
+Установочное присоединение диаметр резьбы: 10
+Установочное присоединение шаг резьбы: 1.0
+Товарное наименование: Пресс-маслёнка угловая 45° с резьбой M10x1 стальная оцинкованная, комплект 10 шт.
+Полное техническое наименование: Пресс-маслёнка угловая 45° с резьбой M10x1 стальная оцинкованная, комплект 10 шт.</t>
+  </si>
+  <si>
+    <t>угловой 45°</t>
+  </si>
+  <si>
+    <t>_44351121742</t>
+  </si>
+  <si>
+    <t>_RD 0010/1</t>
+  </si>
+  <si>
+    <t>Пресс-маслёнка угловая 45° с резьбой M10x1 стальная оцинкованная</t>
+  </si>
+  <si>
+    <t>Вид изделия: Пресс-маслёнка
+Сервисное назначение: смазка
+Каталожная роль: сервисное соединение
+Материал корпуса: сталь
+Вид покрытия: цинковое покрытие
+Количество в товарной позиции: 1 шт.
+Геометрия: угловой 45°
+Установочное присоединение тип: резьба
+Установочное присоединение: НР M10x1
+Установочное присоединение резьба: НР M10x1
+Установочное присоединение исполнение резьбы: НР
+Установочное присоединение тип резьбы: M
+Установочное присоединение диаметр резьбы: 10
+Установочное присоединение шаг резьбы: 1.0
+Товарное наименование: Пресс-маслёнка угловая 45° с резьбой M10x1 стальная оцинкованная
+Полное техническое наименование: Пресс-маслёнка угловая 45° с резьбой M10x1 стальная оцинкованная</t>
+  </si>
+  <si>
+    <t>_1905587013</t>
+  </si>
+  <si>
+    <t>_DK-0002</t>
+  </si>
+  <si>
+    <t>_44141029491</t>
+  </si>
+  <si>
+    <t>_RD-0014</t>
+  </si>
+  <si>
+    <t>Пресс-маслёнка угловая 45° с резьбой M6x1 стальная оцинкованная, комплект 10 шт.</t>
+  </si>
+  <si>
+    <t>Вид изделия: Пресс-маслёнка
+Сервисное назначение: смазка
+Каталожная роль: сервисное соединение
+Материал корпуса: сталь
+Вид покрытия: цинковое покрытие
+Количество в товарной позиции: 10 шт.
+Геометрия: угловой 45°
+Установочное присоединение тип: резьба
+Установочное присоединение: НР M6x1
+Установочное присоединение резьба: НР M6x1
+Установочное присоединение исполнение резьбы: НР
+Установочное присоединение тип резьбы: M
+Установочное присоединение диаметр резьбы: 6
+Установочное присоединение шаг резьбы: 1.0
+Товарное наименование: Пресс-маслёнка угловая 45° с резьбой M6x1 стальная оцинкованная, комплект 10 шт.
+Полное техническое наименование: Пресс-маслёнка угловая 45° с резьбой M6x1 стальная оцинкованная, комплект 10 шт.</t>
+  </si>
+  <si>
+    <t>_44351121737</t>
+  </si>
+  <si>
+    <t>_RD 0006/1</t>
+  </si>
+  <si>
+    <t>Пресс-маслёнка угловая 45° с резьбой M6x1 стальная оцинкованная</t>
+  </si>
+  <si>
+    <t>Вид изделия: Пресс-маслёнка
+Сервисное назначение: смазка
+Каталожная роль: сервисное соединение
+Материал корпуса: сталь
+Вид покрытия: цинковое покрытие
+Количество в товарной позиции: 1 шт.
+Геометрия: угловой 45°
+Установочное присоединение тип: резьба
+Установочное присоединение: НР M6x1
+Установочное присоединение резьба: НР M6x1
+Установочное присоединение исполнение резьбы: НР
+Установочное присоединение тип резьбы: M
+Установочное присоединение диаметр резьбы: 6
+Установочное присоединение шаг резьбы: 1.0
+Товарное наименование: Пресс-маслёнка угловая 45° с резьбой M6x1 стальная оцинкованная
+Полное техническое наименование: Пресс-маслёнка угловая 45° с резьбой M6x1 стальная оцинкованная</t>
+  </si>
+  <si>
+    <t>_1905587016</t>
+  </si>
+  <si>
+    <t>_DK-0005</t>
+  </si>
+  <si>
+    <t>_44141029494</t>
+  </si>
+  <si>
+    <t>_RD-0017</t>
+  </si>
+  <si>
+    <t>Пресс-маслёнка угловая 45° с резьбой M8x1 стальная оцинкованная, комплект 10 шт.</t>
+  </si>
+  <si>
+    <t>Вид изделия: Пресс-маслёнка
+Сервисное назначение: смазка
+Каталожная роль: сервисное соединение
+Материал корпуса: сталь
+Вид покрытия: цинковое покрытие
+Количество в товарной позиции: 10 шт.
+Геометрия: угловой 45°
+Установочное присоединение тип: резьба
+Установочное присоединение: НР M8x1
+Установочное присоединение резьба: НР M8x1
+Установочное присоединение исполнение резьбы: НР
+Установочное присоединение тип резьбы: M
+Установочное присоединение диаметр резьбы: 8
+Установочное присоединение шаг резьбы: 1.0
+Товарное наименование: Пресс-маслёнка угловая 45° с резьбой M8x1 стальная оцинкованная, комплект 10 шт.
+Полное техническое наименование: Пресс-маслёнка угловая 45° с резьбой M8x1 стальная оцинкованная, комплект 10 шт.</t>
+  </si>
+  <si>
+    <t>_1905587019</t>
+  </si>
+  <si>
+    <t>_DK-0008</t>
+  </si>
+  <si>
+    <t>Пресс-маслёнка угловая 45° с резьбой M8x1 стальная оцинкованная</t>
+  </si>
+  <si>
+    <t>Вид изделия: Пресс-маслёнка
+Сервисное назначение: смазка
+Каталожная роль: сервисное соединение
+Материал корпуса: сталь
+Вид покрытия: цинковое покрытие
+Количество в товарной позиции: 1 шт.
+Геометрия: угловой 45°
+Установочное присоединение тип: резьба
+Установочное присоединение: НР M8x1
+Установочное присоединение резьба: НР M8x1
+Установочное присоединение исполнение резьбы: НР
+Установочное присоединение тип резьбы: M
+Установочное присоединение диаметр резьбы: 8
+Установочное присоединение шаг резьбы: 1.0
+Товарное наименование: Пресс-маслёнка угловая 45° с резьбой M8x1 стальная оцинкованная
+Полное техническое наименование: Пресс-маслёнка угловая 45° с резьбой M8x1 стальная оцинкованная</t>
+  </si>
+  <si>
+    <t>_44141029492</t>
+  </si>
+  <si>
+    <t>_RD-0015</t>
+  </si>
+  <si>
+    <t>Пресс-маслёнка угловая 90° с резьбой M6x1 стальная оцинкованная, комплект 10 шт.</t>
+  </si>
+  <si>
+    <t>Вид изделия: Пресс-маслёнка
+Сервисное назначение: смазка
+Каталожная роль: сервисное соединение
+Материал корпуса: сталь
+Вид покрытия: цинковое покрытие
+Количество в товарной позиции: 10 шт.
+Геометрия: угловой 90°
+Установочное присоединение тип: резьба
+Установочное присоединение: НР M6x1
+Установочное присоединение резьба: НР M6x1
+Установочное присоединение исполнение резьбы: НР
+Установочное присоединение тип резьбы: M
+Установочное присоединение диаметр резьбы: 6
+Установочное присоединение шаг резьбы: 1.0
+Товарное наименование: Пресс-маслёнка угловая 90° с резьбой M6x1 стальная оцинкованная, комплект 10 шт.
+Полное техническое наименование: Пресс-маслёнка угловая 90° с резьбой M6x1 стальная оцинкованная, комплект 10 шт.</t>
+  </si>
+  <si>
+    <t>угловой 90°</t>
+  </si>
+  <si>
+    <t>_1905587017</t>
+  </si>
+  <si>
+    <t>_DK-0006</t>
+  </si>
+  <si>
+    <t>Пресс-маслёнка угловая 90° с резьбой M6x1 стальная оцинкованная</t>
+  </si>
+  <si>
+    <t>Вид изделия: Пресс-маслёнка
+Сервисное назначение: смазка
+Каталожная роль: сервисное соединение
+Материал корпуса: сталь
+Вид покрытия: цинковое покрытие
+Количество в товарной позиции: 1 шт.
+Геометрия: угловой 90°
+Установочное присоединение тип: резьба
+Установочное присоединение: НР M6x1
+Установочное присоединение резьба: НР M6x1
+Установочное присоединение исполнение резьбы: НР
+Установочное присоединение тип резьбы: M
+Установочное присоединение диаметр резьбы: 6
+Установочное присоединение шаг резьбы: 1.0
+Товарное наименование: Пресс-маслёнка угловая 90° с резьбой M6x1 стальная оцинкованная
+Полное техническое наименование: Пресс-маслёнка угловая 90° с резьбой M6x1 стальная оцинкованная</t>
+  </si>
+  <si>
+    <t>_44141029495</t>
+  </si>
+  <si>
+    <t>_RD-0018</t>
+  </si>
+  <si>
+    <t>Пресс-маслёнка угловая 90° с резьбой M8x1 стальная оцинкованная, комплект 10 шт.</t>
+  </si>
+  <si>
+    <t>Вид изделия: Пресс-маслёнка
+Сервисное назначение: смазка
+Каталожная роль: сервисное соединение
+Материал корпуса: сталь
+Вид покрытия: цинковое покрытие
+Количество в товарной позиции: 10 шт.
+Геометрия: угловой 90°
+Установочное присоединение тип: резьба
+Установочное присоединение: НР M8x1
+Установочное присоединение резьба: НР M8x1
+Установочное присоединение исполнение резьбы: НР
+Установочное присоединение тип резьбы: M
+Установочное присоединение диаметр резьбы: 8
+Установочное присоединение шаг резьбы: 1.0
+Товарное наименование: Пресс-маслёнка угловая 90° с резьбой M8x1 стальная оцинкованная, комплект 10 шт.
+Полное техническое наименование: Пресс-маслёнка угловая 90° с резьбой M8x1 стальная оцинкованная, комплект 10 шт.</t>
+  </si>
+  <si>
+    <t>_44351121738</t>
+  </si>
+  <si>
+    <t>_RD 0008/1</t>
+  </si>
+  <si>
+    <t>Пресс-маслёнка угловая 90° с резьбой M8x1 стальная оцинкованная</t>
+  </si>
+  <si>
+    <t>Вид изделия: Пресс-маслёнка
+Сервисное назначение: смазка
+Каталожная роль: сервисное соединение
+Материал корпуса: сталь
+Вид покрытия: цинковое покрытие
+Количество в товарной позиции: 1 шт.
+Геометрия: угловой 90°
+Установочное присоединение тип: резьба
+Установочное присоединение: НР M8x1
+Установочное присоединение резьба: НР M8x1
+Установочное присоединение исполнение резьбы: НР
+Установочное присоединение тип резьбы: M
+Установочное присоединение диаметр резьбы: 8
+Установочное присоединение шаг резьбы: 1.0
+Товарное наименование: Пресс-маслёнка угловая 90° с резьбой M8x1 стальная оцинкованная
+Полное техническое наименование: Пресс-маслёнка угловая 90° с резьбой M8x1 стальная оцинкованная</t>
+  </si>
+  <si>
+    <t>_1905587020</t>
+  </si>
+  <si>
+    <t>_DK-0009</t>
+  </si>
+  <si>
+    <t>_44141029489</t>
+  </si>
+  <si>
+    <t>_RD-0012</t>
+  </si>
+  <si>
+    <t>Пресс-маслёнка угловая 90° с резьбой M10x1 стальная оцинкованная, комплект 10 шт.</t>
+  </si>
+  <si>
+    <t>Вид изделия: Пресс-маслёнка
+Сервисное назначение: смазка
+Каталожная роль: сервисное соединение
+Материал корпуса: сталь
+Вид покрытия: цинковое покрытие
+Количество в товарной позиции: 10 шт.
+Геометрия: угловой 90°
+Установочное присоединение тип: резьба
+Установочное присоединение: НР M10x1
+Установочное присоединение резьба: НР M10x1
+Установочное присоединение исполнение резьбы: НР
+Установочное присоединение тип резьбы: M
+Установочное присоединение диаметр резьбы: 10
+Установочное присоединение шаг резьбы: 1.0
+Товарное наименование: Пресс-маслёнка угловая 90° с резьбой M10x1 стальная оцинкованная, комплект 10 шт.
+Полное техническое наименование: Пресс-маслёнка угловая 90° с резьбой M10x1 стальная оцинкованная, комплект 10 шт.</t>
+  </si>
+  <si>
+    <t>_44351121743</t>
+  </si>
+  <si>
+    <t>_RD 0011/1</t>
+  </si>
+  <si>
+    <t>Пресс-маслёнка угловая 90° с резьбой M10x1 стальная оцинкованная</t>
+  </si>
+  <si>
+    <t>Вид изделия: Пресс-маслёнка
+Сервисное назначение: смазка
+Каталожная роль: сервисное соединение
+Материал корпуса: сталь
+Вид покрытия: цинковое покрытие
+Количество в товарной позиции: 1 шт.
+Геометрия: угловой 90°
+Установочное присоединение тип: резьба
+Установочное присоединение: НР M10x1
+Установочное присоединение резьба: НР M10x1
+Установочное присоединение исполнение резьбы: НР
+Установочное присоединение тип резьбы: M
+Установочное присоединение диаметр резьбы: 10
+Установочное присоединение шаг резьбы: 1.0
+Товарное наименование: Пресс-маслёнка угловая 90° с резьбой M10x1 стальная оцинкованная
+Полное техническое наименование: Пресс-маслёнка угловая 90° с резьбой M10x1 стальная оцинкованная</t>
+  </si>
+  <si>
+    <t>_1905587014</t>
+  </si>
+  <si>
+    <t>_DK-0003</t>
+  </si>
+  <si>
+    <t>_44351121739</t>
+  </si>
+  <si>
+    <t>_RD 1118</t>
+  </si>
+  <si>
+    <t>Колпачок защитный для пресс-маслёнки пластиковый красный</t>
+  </si>
+  <si>
+    <t>Вид изделия: Колпачок защитный
+Сервисное назначение: защитный колпачок
+Каталожная роль: компонент сервисного соединителя
+Материал изделия: пластик
+Количество в товарной позиции: 1 шт.
+Применяемость колпачка: для пресс-маслёнки
+Цвет: красный
+Товарное наименование: Колпачок защитный для пресс-маслёнки пластиковый красный
+Полное техническое наименование: Колпачок защитный для пресс-маслёнки пластиковый красный</t>
+  </si>
+  <si>
+    <t>Колпачок защитный</t>
+  </si>
+  <si>
+    <t>защитный колпачок</t>
+  </si>
+  <si>
+    <t>компонент сервисного соединителя</t>
+  </si>
+  <si>
+    <t>для пресс-маслёнки</t>
+  </si>
+  <si>
+    <t>красный</t>
+  </si>
+  <si>
+    <t>_44351121740</t>
+  </si>
+  <si>
+    <t>_RD 1119</t>
+  </si>
+  <si>
+    <t>Колпачок защитный для пресс-маслёнки пластиковый жёлтый</t>
+  </si>
+  <si>
+    <t>Вид изделия: Колпачок защитный
+Сервисное назначение: защитный колпачок
+Каталожная роль: компонент сервисного соединителя
+Материал изделия: пластик
+Количество в товарной позиции: 1 шт.
+Применяемость колпачка: для пресс-маслёнки
+Цвет: жёлтый
+Товарное наименование: Колпачок защитный для пресс-маслёнки пластиковый жёлтый
+Полное техническое наименование: Колпачок защитный для пресс-маслёнки пластиковый жёлтый</t>
+  </si>
+  <si>
+    <t>жёлтый</t>
+  </si>
+  <si>
+    <t>_44351121741</t>
+  </si>
+  <si>
+    <t>_RD 1120</t>
+  </si>
+  <si>
+    <t>Колпачок защитный для пресс-маслёнки пластиковый зелёный</t>
+  </si>
+  <si>
+    <t>Вид изделия: Колпачок защитный
+Сервисное назначение: защитный колпачок
+Каталожная роль: компонент сервисного соединителя
+Материал изделия: пластик
+Количество в товарной позиции: 1 шт.
+Применяемость колпачка: для пресс-маслёнки
+Цвет: зелёный
+Товарное наименование: Колпачок защитный для пресс-маслёнки пластиковый зелёный
+Полное техническое наименование: Колпачок защитный для пресс-маслёнки пластиковый зелёный</t>
+  </si>
+  <si>
+    <t>зелёный</t>
+  </si>
+  <si>
+    <t>Вид покрытия</t>
+  </si>
+  <si>
+    <t>Количество в товарной позиции</t>
+  </si>
+  <si>
+    <t>Материал изделия</t>
+  </si>
+  <si>
+    <t>Применяемость колпачка</t>
+  </si>
+  <si>
+    <t>Цвет</t>
+  </si>
+  <si>
+    <t>Наконечник зажимной для накачки шин угловой 90° со штуцером типа «ёлочка» 6 мм алюминиевый с стальным рычагом</t>
   </si>
   <si>
     <t>Вид изделия: Наконечник зажимной для накачки шин
 Сервисное назначение: накачка шин
 Каталожная роль: сервисное соединение
 Материал корпуса: алюминий
-Геометрия: прямой
+Геометрия: угловой 90°
 Способ фиксации на вентиле: зажимной
 Материал рычага: сталь
 Установочное присоединение тип: штуцер
@@ -620,27 +1292,18 @@
 Установочное присоединение диаметр штуцера, мм: 6
 Установочное присоединение профиль штуцера: елочка
 Тип подключения к вентилю: под автомобильный вентиль
-Товарное наименование: Наконечник зажимной для накачки шин прямой со штуцером типа «ёлочка» 6 мм алюминиевый с стальным рычагом
-Полное техническое наименование: Наконечник зажимной для накачки шин прямой со штуцером типа «ёлочка» 6 мм алюминиевый с стальным рычагом</t>
-  </si>
-  <si>
-    <t>алюминий</t>
-  </si>
-  <si>
-    <t>_44391150033</t>
-  </si>
-  <si>
-    <t>_RD 97.76.43</t>
-  </si>
-  <si>
-    <t>Наконечник зажимной для накачки шин прямой со штуцером типа «ёлочка» 8 мм алюминиевый с стальным рычагом</t>
+Товарное наименование: Наконечник зажимной для накачки шин угловой 90° со штуцером типа «ёлочка» 6 мм алюминиевый с стальным рычагом
+Полное техническое наименование: Наконечник зажимной для накачки шин угловой 90° со штуцером типа «ёлочка» 6 мм алюминиевый с стальным рычагом</t>
+  </si>
+  <si>
+    <t>Наконечник зажимной для накачки шин угловой 90° со штуцером типа «ёлочка» 8 мм алюминиевый с стальным рычагом</t>
   </si>
   <si>
     <t>Вид изделия: Наконечник зажимной для накачки шин
 Сервисное назначение: накачка шин
 Каталожная роль: сервисное соединение
 Материал корпуса: алюминий
-Геометрия: прямой
+Геометрия: угловой 90°
 Способ фиксации на вентиле: зажимной
 Материал рычага: сталь
 Установочное присоединение тип: штуцер
@@ -648,24 +1311,18 @@
 Установочное присоединение диаметр штуцера, мм: 8
 Установочное присоединение профиль штуцера: елочка
 Тип подключения к вентилю: под автомобильный вентиль
-Товарное наименование: Наконечник зажимной для накачки шин прямой со штуцером типа «ёлочка» 8 мм алюминиевый с стальным рычагом
-Полное техническое наименование: Наконечник зажимной для накачки шин прямой со штуцером типа «ёлочка» 8 мм алюминиевый с стальным рычагом</t>
-  </si>
-  <si>
-    <t>_44391150034</t>
-  </si>
-  <si>
-    <t>_RD 97.76.44</t>
-  </si>
-  <si>
-    <t>Наконечник зажимной для накачки шин прямой со штуцером типа «ёлочка» 6 мм алюминиевый с пластиковым рычагом</t>
+Товарное наименование: Наконечник зажимной для накачки шин угловой 90° со штуцером типа «ёлочка» 8 мм алюминиевый с стальным рычагом
+Полное техническое наименование: Наконечник зажимной для накачки шин угловой 90° со штуцером типа «ёлочка» 8 мм алюминиевый с стальным рычагом</t>
+  </si>
+  <si>
+    <t>Наконечник зажимной для накачки шин угловой 90° со штуцером типа «ёлочка» 6 мм алюминиевый с пластиковым рычагом</t>
   </si>
   <si>
     <t>Вид изделия: Наконечник зажимной для накачки шин
 Сервисное назначение: накачка шин
 Каталожная роль: сервисное соединение
 Материал корпуса: алюминий
-Геометрия: прямой
+Геометрия: угловой 90°
 Способ фиксации на вентиле: зажимной
 Материал рычага: пластик
 Установочное присоединение тип: штуцер
@@ -673,27 +1330,18 @@
 Установочное присоединение диаметр штуцера, мм: 6
 Установочное присоединение профиль штуцера: елочка
 Тип подключения к вентилю: под автомобильный вентиль
-Товарное наименование: Наконечник зажимной для накачки шин прямой со штуцером типа «ёлочка» 6 мм алюминиевый с пластиковым рычагом
-Полное техническое наименование: Наконечник зажимной для накачки шин прямой со штуцером типа «ёлочка» 6 мм алюминиевый с пластиковым рычагом</t>
-  </si>
-  <si>
-    <t>пластик</t>
-  </si>
-  <si>
-    <t>_44391150035</t>
-  </si>
-  <si>
-    <t>_RD 97.76.45</t>
-  </si>
-  <si>
-    <t>Наконечник зажимной для накачки шин прямой со штуцером типа «ёлочка» 8 мм алюминиевый с пластиковым рычагом</t>
+Товарное наименование: Наконечник зажимной для накачки шин угловой 90° со штуцером типа «ёлочка» 6 мм алюминиевый с пластиковым рычагом
+Полное техническое наименование: Наконечник зажимной для накачки шин угловой 90° со штуцером типа «ёлочка» 6 мм алюминиевый с пластиковым рычагом</t>
+  </si>
+  <si>
+    <t>Наконечник зажимной для накачки шин угловой 90° со штуцером типа «ёлочка» 8 мм алюминиевый с пластиковым рычагом</t>
   </si>
   <si>
     <t>Вид изделия: Наконечник зажимной для накачки шин
 Сервисное назначение: накачка шин
 Каталожная роль: сервисное соединение
 Материал корпуса: алюминий
-Геометрия: прямой
+Геометрия: угловой 90°
 Способ фиксации на вентиле: зажимной
 Материал рычага: пластик
 Установочное присоединение тип: штуцер
@@ -701,11 +1349,44 @@
 Установочное присоединение диаметр штуцера, мм: 8
 Установочное присоединение профиль штуцера: елочка
 Тип подключения к вентилю: под автомобильный вентиль
-Товарное наименование: Наконечник зажимной для накачки шин прямой со штуцером типа «ёлочка» 8 мм алюминиевый с пластиковым рычагом
-Полное техническое наименование: Наконечник зажимной для накачки шин прямой со штуцером типа «ёлочка» 8 мм алюминиевый с пластиковым рычагом</t>
-  </si>
-  <si>
-    <t>Номер группы ch3</t>
+Товарное наименование: Наконечник зажимной для накачки шин угловой 90° со штуцером типа «ёлочка» 8 мм алюминиевый с пластиковым рычагом
+Полное техническое наименование: Наконечник зажимной для накачки шин угловой 90° со штуцером типа «ёлочка» 8 мм алюминиевый с пластиковым рычагом</t>
+  </si>
+  <si>
+    <t>_44351237331</t>
+  </si>
+  <si>
+    <t>_RD 57.53.87</t>
+  </si>
+  <si>
+    <t>_44351237332</t>
+  </si>
+  <si>
+    <t>_RD 57.53.88</t>
+  </si>
+  <si>
+    <t>_44351237333</t>
+  </si>
+  <si>
+    <t>_RD 57.53.89</t>
+  </si>
+  <si>
+    <t>_44351237334</t>
+  </si>
+  <si>
+    <t>_RD 57.53.90</t>
+  </si>
+  <si>
+    <t>Наконечник шланга підкачки (гайка-баранчик) штуцер 6мм (RIDER)</t>
+  </si>
+  <si>
+    <t>Наконечник шланга підкачки (гайка-баранчик) штуцер 8мм (RIDER)</t>
+  </si>
+  <si>
+    <t>Наконечник шланга підкачування (гайка-баранчик) штуцер 10мм (RIDER)</t>
+  </si>
+  <si>
+    <t>Наконечник шланга підкачки (гайка-баранчик) штуцер 12мм (RIDER)</t>
   </si>
 </sst>
 </file>
@@ -725,6 +1406,8 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
@@ -764,7 +1447,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -775,6 +1458,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Звичайний" xfId="0" builtinId="0"/>
@@ -1089,10 +1773,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3118E0D-448D-4EEB-9348-1247B3113B2C}">
-  <dimension ref="A1:AE29"/>
+  <dimension ref="A1:AJ62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:31" ht="105" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" ht="105" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1183,11 +1867,26 @@
       <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="3" t="s">
-        <v>150</v>
+      <c r="AE1" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="AJ1" s="3" t="s">
+        <v>142</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>30</v>
       </c>
@@ -1254,11 +1953,16 @@
       <c r="AB2" s="2"/>
       <c r="AC2" s="2"/>
       <c r="AD2" s="2"/>
-      <c r="AE2">
+      <c r="AE2" s="2"/>
+      <c r="AF2" s="2"/>
+      <c r="AG2" s="2"/>
+      <c r="AH2" s="2"/>
+      <c r="AI2" s="2"/>
+      <c r="AJ2">
         <v>129</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>45</v>
       </c>
@@ -1325,11 +2029,16 @@
       <c r="AB3" s="2"/>
       <c r="AC3" s="2"/>
       <c r="AD3" s="2"/>
-      <c r="AE3">
+      <c r="AE3" s="2"/>
+      <c r="AF3" s="2"/>
+      <c r="AG3" s="2"/>
+      <c r="AH3" s="2"/>
+      <c r="AI3" s="2"/>
+      <c r="AJ3">
         <v>129</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>47</v>
       </c>
@@ -1396,11 +2105,16 @@
       <c r="AB4" s="2"/>
       <c r="AC4" s="2"/>
       <c r="AD4" s="2"/>
-      <c r="AE4">
+      <c r="AE4" s="2"/>
+      <c r="AF4" s="2"/>
+      <c r="AG4" s="2"/>
+      <c r="AH4" s="2"/>
+      <c r="AI4" s="2"/>
+      <c r="AJ4">
         <v>129</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>49</v>
       </c>
@@ -1467,11 +2181,16 @@
       <c r="AB5" s="2"/>
       <c r="AC5" s="2"/>
       <c r="AD5" s="2"/>
-      <c r="AE5">
+      <c r="AE5" s="2"/>
+      <c r="AF5" s="2"/>
+      <c r="AG5" s="2"/>
+      <c r="AH5" s="2"/>
+      <c r="AI5" s="2"/>
+      <c r="AJ5">
         <v>129</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>51</v>
       </c>
@@ -1538,11 +2257,16 @@
       <c r="AB6" s="2"/>
       <c r="AC6" s="2"/>
       <c r="AD6" s="2"/>
-      <c r="AE6">
+      <c r="AE6" s="2"/>
+      <c r="AF6" s="2"/>
+      <c r="AG6" s="2"/>
+      <c r="AH6" s="2"/>
+      <c r="AI6" s="2"/>
+      <c r="AJ6">
         <v>129</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>56</v>
       </c>
@@ -1609,11 +2333,16 @@
       <c r="AB7" s="2"/>
       <c r="AC7" s="2"/>
       <c r="AD7" s="2"/>
-      <c r="AE7">
+      <c r="AE7" s="2"/>
+      <c r="AF7" s="2"/>
+      <c r="AG7" s="2"/>
+      <c r="AH7" s="2"/>
+      <c r="AI7" s="2"/>
+      <c r="AJ7">
         <v>129</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>58</v>
       </c>
@@ -1680,11 +2409,16 @@
       <c r="AB8" s="2"/>
       <c r="AC8" s="2"/>
       <c r="AD8" s="2"/>
-      <c r="AE8">
+      <c r="AE8" s="2"/>
+      <c r="AF8" s="2"/>
+      <c r="AG8" s="2"/>
+      <c r="AH8" s="2"/>
+      <c r="AI8" s="2"/>
+      <c r="AJ8">
         <v>129</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>60</v>
       </c>
@@ -1751,11 +2485,16 @@
       <c r="AB9" s="2"/>
       <c r="AC9" s="2"/>
       <c r="AD9" s="2"/>
-      <c r="AE9">
+      <c r="AE9" s="2"/>
+      <c r="AF9" s="2"/>
+      <c r="AG9" s="2"/>
+      <c r="AH9" s="2"/>
+      <c r="AI9" s="2"/>
+      <c r="AJ9">
         <v>129</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>62</v>
       </c>
@@ -1822,11 +2561,16 @@
       <c r="AB10" s="2"/>
       <c r="AC10" s="2"/>
       <c r="AD10" s="2"/>
-      <c r="AE10">
+      <c r="AE10" s="2"/>
+      <c r="AF10" s="2"/>
+      <c r="AG10" s="2"/>
+      <c r="AH10" s="2"/>
+      <c r="AI10" s="2"/>
+      <c r="AJ10">
         <v>129</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>64</v>
       </c>
@@ -1893,11 +2637,16 @@
       <c r="AB11" s="2"/>
       <c r="AC11" s="2"/>
       <c r="AD11" s="2"/>
-      <c r="AE11">
+      <c r="AE11" s="2"/>
+      <c r="AF11" s="2"/>
+      <c r="AG11" s="2"/>
+      <c r="AH11" s="2"/>
+      <c r="AI11" s="2"/>
+      <c r="AJ11">
         <v>129</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>66</v>
       </c>
@@ -1970,11 +2719,16 @@
       <c r="AB12" s="2"/>
       <c r="AC12" s="2"/>
       <c r="AD12" s="2"/>
-      <c r="AE12">
+      <c r="AE12" s="2"/>
+      <c r="AF12" s="2"/>
+      <c r="AG12" s="2"/>
+      <c r="AH12" s="2"/>
+      <c r="AI12" s="2"/>
+      <c r="AJ12">
         <v>130</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>76</v>
       </c>
@@ -2047,11 +2801,16 @@
       <c r="AB13" s="2"/>
       <c r="AC13" s="2"/>
       <c r="AD13" s="2"/>
-      <c r="AE13">
+      <c r="AE13" s="2"/>
+      <c r="AF13" s="2"/>
+      <c r="AG13" s="2"/>
+      <c r="AH13" s="2"/>
+      <c r="AI13" s="2"/>
+      <c r="AJ13">
         <v>130</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>82</v>
       </c>
@@ -2122,11 +2881,16 @@
       <c r="AB14" s="2"/>
       <c r="AC14" s="2"/>
       <c r="AD14" s="2"/>
-      <c r="AE14">
+      <c r="AE14" s="2"/>
+      <c r="AF14" s="2"/>
+      <c r="AG14" s="2"/>
+      <c r="AH14" s="2"/>
+      <c r="AI14" s="2"/>
+      <c r="AJ14">
         <v>130</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>87</v>
       </c>
@@ -2197,11 +2961,16 @@
       <c r="AB15" s="2"/>
       <c r="AC15" s="2"/>
       <c r="AD15" s="2"/>
-      <c r="AE15">
+      <c r="AE15" s="2"/>
+      <c r="AF15" s="2"/>
+      <c r="AG15" s="2"/>
+      <c r="AH15" s="2"/>
+      <c r="AI15" s="2"/>
+      <c r="AJ15">
         <v>130</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>91</v>
       </c>
@@ -2274,11 +3043,16 @@
       <c r="AB16" s="2"/>
       <c r="AC16" s="2"/>
       <c r="AD16" s="2"/>
-      <c r="AE16">
+      <c r="AE16" s="2"/>
+      <c r="AF16" s="2"/>
+      <c r="AG16" s="2"/>
+      <c r="AH16" s="2"/>
+      <c r="AI16" s="2"/>
+      <c r="AJ16">
         <v>130</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>95</v>
       </c>
@@ -2351,11 +3125,16 @@
       <c r="AB17" s="2"/>
       <c r="AC17" s="2"/>
       <c r="AD17" s="2"/>
-      <c r="AE17">
+      <c r="AE17" s="2"/>
+      <c r="AF17" s="2"/>
+      <c r="AG17" s="2"/>
+      <c r="AH17" s="2"/>
+      <c r="AI17" s="2"/>
+      <c r="AJ17">
         <v>130</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>99</v>
       </c>
@@ -2428,11 +3207,16 @@
       <c r="AB18" s="2"/>
       <c r="AC18" s="2"/>
       <c r="AD18" s="2"/>
-      <c r="AE18">
+      <c r="AE18" s="2"/>
+      <c r="AF18" s="2"/>
+      <c r="AG18" s="2"/>
+      <c r="AH18" s="2"/>
+      <c r="AI18" s="2"/>
+      <c r="AJ18">
         <v>130</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>101</v>
       </c>
@@ -2505,11 +3289,16 @@
       <c r="AB19" s="2"/>
       <c r="AC19" s="2"/>
       <c r="AD19" s="2"/>
-      <c r="AE19">
+      <c r="AE19" s="2"/>
+      <c r="AF19" s="2"/>
+      <c r="AG19" s="2"/>
+      <c r="AH19" s="2"/>
+      <c r="AI19" s="2"/>
+      <c r="AJ19">
         <v>130</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>103</v>
       </c>
@@ -2574,11 +3363,16 @@
       <c r="AD20" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="AE20">
+      <c r="AE20" s="2"/>
+      <c r="AF20" s="2"/>
+      <c r="AG20" s="2"/>
+      <c r="AH20" s="2"/>
+      <c r="AI20" s="2"/>
+      <c r="AJ20">
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>115</v>
       </c>
@@ -2643,11 +3437,16 @@
       <c r="AD21" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="AE21">
+      <c r="AE21" s="2"/>
+      <c r="AF21" s="2"/>
+      <c r="AG21" s="2"/>
+      <c r="AH21" s="2"/>
+      <c r="AI21" s="2"/>
+      <c r="AJ21">
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>120</v>
       </c>
@@ -2712,11 +3511,16 @@
       <c r="AD22" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="AE22">
+      <c r="AE22" s="2"/>
+      <c r="AF22" s="2"/>
+      <c r="AG22" s="2"/>
+      <c r="AH22" s="2"/>
+      <c r="AI22" s="2"/>
+      <c r="AJ22">
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>122</v>
       </c>
@@ -2781,11 +3585,16 @@
       <c r="AD23" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="AE23">
+      <c r="AE23" s="2"/>
+      <c r="AF23" s="2"/>
+      <c r="AG23" s="2"/>
+      <c r="AH23" s="2"/>
+      <c r="AI23" s="2"/>
+      <c r="AJ23">
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>126</v>
       </c>
@@ -2850,11 +3659,16 @@
       <c r="AD24" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="AE24">
+      <c r="AE24" s="2"/>
+      <c r="AF24" s="2"/>
+      <c r="AG24" s="2"/>
+      <c r="AH24" s="2"/>
+      <c r="AI24" s="2"/>
+      <c r="AJ24">
         <v>76</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>130</v>
       </c>
@@ -2919,11 +3733,16 @@
       <c r="AD25" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="AE25">
+      <c r="AE25" s="2"/>
+      <c r="AF25" s="2"/>
+      <c r="AG25" s="2"/>
+      <c r="AH25" s="2"/>
+      <c r="AI25" s="2"/>
+      <c r="AJ25">
         <v>76</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>132</v>
       </c>
@@ -2931,13 +3750,13 @@
         <v>133</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>134</v>
+        <v>260</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>134</v>
+        <v>260</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>135</v>
+        <v>261</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2" t="s">
@@ -2950,7 +3769,7 @@
         <v>36</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
@@ -2971,7 +3790,7 @@
       <c r="W26" s="2"/>
       <c r="X26" s="2"/>
       <c r="Y26" s="2" t="s">
-        <v>111</v>
+        <v>211</v>
       </c>
       <c r="Z26" s="2" t="s">
         <v>112</v>
@@ -2988,25 +3807,30 @@
       <c r="AD26" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="AE26">
+      <c r="AE26" s="2"/>
+      <c r="AF26" s="2"/>
+      <c r="AG26" s="2"/>
+      <c r="AH26" s="2"/>
+      <c r="AI26" s="2"/>
+      <c r="AJ26">
         <v>77</v>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>139</v>
+        <v>262</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>139</v>
+        <v>262</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>140</v>
+        <v>263</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2" t="s">
@@ -3019,7 +3843,7 @@
         <v>36</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
@@ -3040,7 +3864,7 @@
       <c r="W27" s="2"/>
       <c r="X27" s="2"/>
       <c r="Y27" s="2" t="s">
-        <v>111</v>
+        <v>211</v>
       </c>
       <c r="Z27" s="2" t="s">
         <v>112</v>
@@ -3057,25 +3881,30 @@
       <c r="AD27" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="AE27">
+      <c r="AE27" s="2"/>
+      <c r="AF27" s="2"/>
+      <c r="AG27" s="2"/>
+      <c r="AH27" s="2"/>
+      <c r="AI27" s="2"/>
+      <c r="AJ27">
         <v>77</v>
       </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>143</v>
+        <v>264</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>143</v>
+        <v>264</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>144</v>
+        <v>265</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2" t="s">
@@ -3088,7 +3917,7 @@
         <v>36</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
@@ -3109,13 +3938,13 @@
       <c r="W28" s="2"/>
       <c r="X28" s="2"/>
       <c r="Y28" s="2" t="s">
-        <v>111</v>
+        <v>211</v>
       </c>
       <c r="Z28" s="2" t="s">
         <v>112</v>
       </c>
       <c r="AA28" s="2" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="AB28" s="2">
         <v>6</v>
@@ -3126,47 +3955,34 @@
       <c r="AD28" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="AE28">
+      <c r="AE28" s="2"/>
+      <c r="AF28" s="2"/>
+      <c r="AG28" s="2"/>
+      <c r="AH28" s="2"/>
+      <c r="AI28" s="2"/>
+      <c r="AJ28">
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>149</v>
-      </c>
+    <row r="29" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>268</v>
+      </c>
+      <c r="B29" t="s">
+        <v>269</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
       <c r="F29" s="2"/>
-      <c r="G29" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>136</v>
-      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
-      <c r="M29" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="N29" s="2" t="s">
-        <v>119</v>
-      </c>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" s="2"/>
       <c r="Q29" s="2"/>
@@ -3177,26 +3993,2189 @@
       <c r="V29" s="2"/>
       <c r="W29" s="2"/>
       <c r="X29" s="2"/>
-      <c r="Y29" s="2" t="s">
+      <c r="Y29" s="2"/>
+      <c r="Z29" s="2"/>
+      <c r="AA29" s="2"/>
+      <c r="AB29" s="2"/>
+      <c r="AC29" s="2"/>
+      <c r="AD29" s="2"/>
+      <c r="AE29" s="2"/>
+      <c r="AF29" s="2"/>
+      <c r="AG29" s="2"/>
+      <c r="AH29" s="2"/>
+      <c r="AI29" s="2"/>
+      <c r="AJ29">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="30" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>270</v>
+      </c>
+      <c r="B30" t="s">
+        <v>271</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="2"/>
+      <c r="S30" s="2"/>
+      <c r="T30" s="2"/>
+      <c r="U30" s="2"/>
+      <c r="V30" s="2"/>
+      <c r="W30" s="2"/>
+      <c r="X30" s="2"/>
+      <c r="Y30" s="2"/>
+      <c r="Z30" s="2"/>
+      <c r="AA30" s="2"/>
+      <c r="AB30" s="2"/>
+      <c r="AC30" s="2"/>
+      <c r="AD30" s="2"/>
+      <c r="AE30" s="2"/>
+      <c r="AF30" s="2"/>
+      <c r="AG30" s="2"/>
+      <c r="AH30" s="2"/>
+      <c r="AI30" s="2"/>
+      <c r="AJ30">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="31" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>272</v>
+      </c>
+      <c r="B31" t="s">
+        <v>273</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
+      <c r="R31" s="2"/>
+      <c r="S31" s="2"/>
+      <c r="T31" s="2"/>
+      <c r="U31" s="2"/>
+      <c r="V31" s="2"/>
+      <c r="W31" s="2"/>
+      <c r="X31" s="2"/>
+      <c r="Y31" s="2"/>
+      <c r="Z31" s="2"/>
+      <c r="AA31" s="2"/>
+      <c r="AB31" s="2"/>
+      <c r="AC31" s="2"/>
+      <c r="AD31" s="2"/>
+      <c r="AE31" s="2"/>
+      <c r="AF31" s="2"/>
+      <c r="AG31" s="2"/>
+      <c r="AH31" s="2"/>
+      <c r="AI31" s="2"/>
+      <c r="AJ31">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="32" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>274</v>
+      </c>
+      <c r="B32" t="s">
+        <v>275</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" s="2"/>
+      <c r="Q32" s="2"/>
+      <c r="R32" s="2"/>
+      <c r="S32" s="2"/>
+      <c r="T32" s="2"/>
+      <c r="U32" s="2"/>
+      <c r="V32" s="2"/>
+      <c r="W32" s="2"/>
+      <c r="X32" s="2"/>
+      <c r="Y32" s="2"/>
+      <c r="Z32" s="2"/>
+      <c r="AA32" s="2"/>
+      <c r="AB32" s="2"/>
+      <c r="AC32" s="2"/>
+      <c r="AD32" s="2"/>
+      <c r="AE32" s="2"/>
+      <c r="AF32" s="2"/>
+      <c r="AG32" s="2"/>
+      <c r="AH32" s="2"/>
+      <c r="AI32" s="2"/>
+      <c r="AJ32">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="N33" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="O33" s="2"/>
+      <c r="P33" s="2"/>
+      <c r="Q33" s="2"/>
+      <c r="R33" s="2"/>
+      <c r="S33" s="2"/>
+      <c r="T33" s="2"/>
+      <c r="U33" s="2"/>
+      <c r="V33" s="2"/>
+      <c r="W33" s="2"/>
+      <c r="X33" s="2"/>
+      <c r="Y33" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="Z33" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="AA33" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="AB33" s="2">
+        <v>8</v>
+      </c>
+      <c r="AC33" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD33" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="AE33" s="2"/>
+      <c r="AF33" s="2"/>
+      <c r="AG33" s="2"/>
+      <c r="AH33" s="2"/>
+      <c r="AI33" s="2"/>
+      <c r="AJ33">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="34" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N34" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="O34" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="P34" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q34" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R34" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="S34" s="2">
+        <v>1</v>
+      </c>
+      <c r="T34" s="2"/>
+      <c r="U34" s="2"/>
+      <c r="V34" s="2"/>
+      <c r="W34" s="2"/>
+      <c r="X34" s="2"/>
+      <c r="Y34" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="Z29" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="AA29" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="AB29" s="2">
-        <v>8</v>
-      </c>
-      <c r="AC29" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="AD29" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="AE29">
-        <v>78</v>
+      <c r="Z34" s="2"/>
+      <c r="AA34" s="2"/>
+      <c r="AB34" s="2"/>
+      <c r="AC34" s="2"/>
+      <c r="AD34" s="2"/>
+      <c r="AE34" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="AF34" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="AG34" s="2"/>
+      <c r="AH34" s="2"/>
+      <c r="AI34" s="2"/>
+      <c r="AJ34" s="4">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="35" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N35" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="O35" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="P35" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q35" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R35" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="S35" s="2">
+        <v>1</v>
+      </c>
+      <c r="T35" s="2"/>
+      <c r="U35" s="2"/>
+      <c r="V35" s="2"/>
+      <c r="W35" s="2"/>
+      <c r="X35" s="2"/>
+      <c r="Y35" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="Z35" s="2"/>
+      <c r="AA35" s="2"/>
+      <c r="AB35" s="2"/>
+      <c r="AC35" s="2"/>
+      <c r="AD35" s="2"/>
+      <c r="AE35" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="AF35" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="AG35" s="2"/>
+      <c r="AH35" s="2"/>
+      <c r="AI35" s="2"/>
+      <c r="AJ35" s="4">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="36" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N36" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="O36" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="P36" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q36" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R36" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="S36" s="2">
+        <v>1</v>
+      </c>
+      <c r="T36" s="2"/>
+      <c r="U36" s="2"/>
+      <c r="V36" s="2"/>
+      <c r="W36" s="2"/>
+      <c r="X36" s="2"/>
+      <c r="Y36" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="Z36" s="2"/>
+      <c r="AA36" s="2"/>
+      <c r="AB36" s="2"/>
+      <c r="AC36" s="2"/>
+      <c r="AD36" s="2"/>
+      <c r="AE36" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="AF36" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="AG36" s="2"/>
+      <c r="AH36" s="2"/>
+      <c r="AI36" s="2"/>
+      <c r="AJ36" s="4">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="37" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N37" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="O37" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="P37" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q37" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R37" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="S37" s="2">
+        <v>1</v>
+      </c>
+      <c r="T37" s="2"/>
+      <c r="U37" s="2"/>
+      <c r="V37" s="2"/>
+      <c r="W37" s="2"/>
+      <c r="X37" s="2"/>
+      <c r="Y37" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="Z37" s="2"/>
+      <c r="AA37" s="2"/>
+      <c r="AB37" s="2"/>
+      <c r="AC37" s="2"/>
+      <c r="AD37" s="2"/>
+      <c r="AE37" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="AF37" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="AG37" s="2"/>
+      <c r="AH37" s="2"/>
+      <c r="AI37" s="2"/>
+      <c r="AJ37" s="4">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="38" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="P38" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q38" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R38" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="S38" s="2">
+        <v>1</v>
+      </c>
+      <c r="T38" s="2"/>
+      <c r="U38" s="2"/>
+      <c r="V38" s="2"/>
+      <c r="W38" s="2"/>
+      <c r="X38" s="2"/>
+      <c r="Y38" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="Z38" s="2"/>
+      <c r="AA38" s="2"/>
+      <c r="AB38" s="2"/>
+      <c r="AC38" s="2"/>
+      <c r="AD38" s="2"/>
+      <c r="AE38" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="AF38" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="AG38" s="2"/>
+      <c r="AH38" s="2"/>
+      <c r="AI38" s="2"/>
+      <c r="AJ38" s="4">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="39" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N39" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="O39" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="P39" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q39" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R39" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="S39" s="2">
+        <v>1</v>
+      </c>
+      <c r="T39" s="2"/>
+      <c r="U39" s="2"/>
+      <c r="V39" s="2"/>
+      <c r="W39" s="2"/>
+      <c r="X39" s="2"/>
+      <c r="Y39" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="Z39" s="2"/>
+      <c r="AA39" s="2"/>
+      <c r="AB39" s="2"/>
+      <c r="AC39" s="2"/>
+      <c r="AD39" s="2"/>
+      <c r="AE39" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="AF39" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="AG39" s="2"/>
+      <c r="AH39" s="2"/>
+      <c r="AI39" s="2"/>
+      <c r="AJ39" s="4">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="40" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N40" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="O40" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="P40" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q40" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R40" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="S40" s="2">
+        <v>1</v>
+      </c>
+      <c r="T40" s="2"/>
+      <c r="U40" s="2"/>
+      <c r="V40" s="2"/>
+      <c r="W40" s="2"/>
+      <c r="X40" s="2"/>
+      <c r="Y40" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="Z40" s="2"/>
+      <c r="AA40" s="2"/>
+      <c r="AB40" s="2"/>
+      <c r="AC40" s="2"/>
+      <c r="AD40" s="2"/>
+      <c r="AE40" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="AF40" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="AG40" s="2"/>
+      <c r="AH40" s="2"/>
+      <c r="AI40" s="2"/>
+      <c r="AJ40" s="4">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="41" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N41" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="O41" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="P41" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q41" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R41" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="S41" s="2">
+        <v>1</v>
+      </c>
+      <c r="T41" s="2"/>
+      <c r="U41" s="2"/>
+      <c r="V41" s="2"/>
+      <c r="W41" s="2"/>
+      <c r="X41" s="2"/>
+      <c r="Y41" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="Z41" s="2"/>
+      <c r="AA41" s="2"/>
+      <c r="AB41" s="2"/>
+      <c r="AC41" s="2"/>
+      <c r="AD41" s="2"/>
+      <c r="AE41" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="AF41" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="AG41" s="2"/>
+      <c r="AH41" s="2"/>
+      <c r="AI41" s="2"/>
+      <c r="AJ41" s="4">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="42" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K42" s="2"/>
+      <c r="L42" s="2"/>
+      <c r="M42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N42" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="O42" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="P42" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q42" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R42" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="S42" s="2">
+        <v>1</v>
+      </c>
+      <c r="T42" s="2"/>
+      <c r="U42" s="2"/>
+      <c r="V42" s="2"/>
+      <c r="W42" s="2"/>
+      <c r="X42" s="2"/>
+      <c r="Y42" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="Z42" s="2"/>
+      <c r="AA42" s="2"/>
+      <c r="AB42" s="2"/>
+      <c r="AC42" s="2"/>
+      <c r="AD42" s="2"/>
+      <c r="AE42" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="AF42" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="AG42" s="2"/>
+      <c r="AH42" s="2"/>
+      <c r="AI42" s="2"/>
+      <c r="AJ42" s="4">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="43" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K43" s="2"/>
+      <c r="L43" s="2"/>
+      <c r="M43" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N43" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="O43" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="P43" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q43" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R43" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="S43" s="2">
+        <v>1</v>
+      </c>
+      <c r="T43" s="2"/>
+      <c r="U43" s="2"/>
+      <c r="V43" s="2"/>
+      <c r="W43" s="2"/>
+      <c r="X43" s="2"/>
+      <c r="Y43" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="Z43" s="2"/>
+      <c r="AA43" s="2"/>
+      <c r="AB43" s="2"/>
+      <c r="AC43" s="2"/>
+      <c r="AD43" s="2"/>
+      <c r="AE43" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="AF43" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="AG43" s="2"/>
+      <c r="AH43" s="2"/>
+      <c r="AI43" s="2"/>
+      <c r="AJ43" s="4">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="44" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K44" s="2"/>
+      <c r="L44" s="2"/>
+      <c r="M44" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N44" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="O44" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="P44" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q44" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R44" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="S44" s="2">
+        <v>1</v>
+      </c>
+      <c r="T44" s="2"/>
+      <c r="U44" s="2"/>
+      <c r="V44" s="2"/>
+      <c r="W44" s="2"/>
+      <c r="X44" s="2"/>
+      <c r="Y44" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="Z44" s="2"/>
+      <c r="AA44" s="2"/>
+      <c r="AB44" s="2"/>
+      <c r="AC44" s="2"/>
+      <c r="AD44" s="2"/>
+      <c r="AE44" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="AF44" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="AG44" s="2"/>
+      <c r="AH44" s="2"/>
+      <c r="AI44" s="2"/>
+      <c r="AJ44" s="4">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="45" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K45" s="2"/>
+      <c r="L45" s="2"/>
+      <c r="M45" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N45" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="O45" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="P45" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q45" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R45" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="S45" s="2">
+        <v>1</v>
+      </c>
+      <c r="T45" s="2"/>
+      <c r="U45" s="2"/>
+      <c r="V45" s="2"/>
+      <c r="W45" s="2"/>
+      <c r="X45" s="2"/>
+      <c r="Y45" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="Z45" s="2"/>
+      <c r="AA45" s="2"/>
+      <c r="AB45" s="2"/>
+      <c r="AC45" s="2"/>
+      <c r="AD45" s="2"/>
+      <c r="AE45" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="AF45" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="AG45" s="2"/>
+      <c r="AH45" s="2"/>
+      <c r="AI45" s="2"/>
+      <c r="AJ45" s="4">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="46" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K46" s="2"/>
+      <c r="L46" s="2"/>
+      <c r="M46" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N46" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="O46" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="P46" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q46" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R46" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="S46" s="2">
+        <v>1</v>
+      </c>
+      <c r="T46" s="2"/>
+      <c r="U46" s="2"/>
+      <c r="V46" s="2"/>
+      <c r="W46" s="2"/>
+      <c r="X46" s="2"/>
+      <c r="Y46" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="Z46" s="2"/>
+      <c r="AA46" s="2"/>
+      <c r="AB46" s="2"/>
+      <c r="AC46" s="2"/>
+      <c r="AD46" s="2"/>
+      <c r="AE46" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="AF46" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="AG46" s="2"/>
+      <c r="AH46" s="2"/>
+      <c r="AI46" s="2"/>
+      <c r="AJ46" s="4">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="47" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K47" s="2"/>
+      <c r="L47" s="2"/>
+      <c r="M47" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N47" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="O47" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="P47" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q47" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R47" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="S47" s="2">
+        <v>1</v>
+      </c>
+      <c r="T47" s="2"/>
+      <c r="U47" s="2"/>
+      <c r="V47" s="2"/>
+      <c r="W47" s="2"/>
+      <c r="X47" s="2"/>
+      <c r="Y47" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="Z47" s="2"/>
+      <c r="AA47" s="2"/>
+      <c r="AB47" s="2"/>
+      <c r="AC47" s="2"/>
+      <c r="AD47" s="2"/>
+      <c r="AE47" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="AF47" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="AG47" s="2"/>
+      <c r="AH47" s="2"/>
+      <c r="AI47" s="2"/>
+      <c r="AJ47" s="4">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="48" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K48" s="2"/>
+      <c r="L48" s="2"/>
+      <c r="M48" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N48" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="O48" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="P48" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q48" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R48" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="S48" s="2">
+        <v>1</v>
+      </c>
+      <c r="T48" s="2"/>
+      <c r="U48" s="2"/>
+      <c r="V48" s="2"/>
+      <c r="W48" s="2"/>
+      <c r="X48" s="2"/>
+      <c r="Y48" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="Z48" s="2"/>
+      <c r="AA48" s="2"/>
+      <c r="AB48" s="2"/>
+      <c r="AC48" s="2"/>
+      <c r="AD48" s="2"/>
+      <c r="AE48" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="AF48" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="AG48" s="2"/>
+      <c r="AH48" s="2"/>
+      <c r="AI48" s="2"/>
+      <c r="AJ48" s="4">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="49" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K49" s="2"/>
+      <c r="L49" s="2"/>
+      <c r="M49" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N49" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="O49" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="P49" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q49" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R49" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="S49" s="2">
+        <v>1</v>
+      </c>
+      <c r="T49" s="2"/>
+      <c r="U49" s="2"/>
+      <c r="V49" s="2"/>
+      <c r="W49" s="2"/>
+      <c r="X49" s="2"/>
+      <c r="Y49" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="Z49" s="2"/>
+      <c r="AA49" s="2"/>
+      <c r="AB49" s="2"/>
+      <c r="AC49" s="2"/>
+      <c r="AD49" s="2"/>
+      <c r="AE49" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="AF49" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="AG49" s="2"/>
+      <c r="AH49" s="2"/>
+      <c r="AI49" s="2"/>
+      <c r="AJ49" s="4">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="50" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K50" s="2"/>
+      <c r="L50" s="2"/>
+      <c r="M50" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N50" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="O50" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="P50" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q50" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R50" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="S50" s="2">
+        <v>1</v>
+      </c>
+      <c r="T50" s="2"/>
+      <c r="U50" s="2"/>
+      <c r="V50" s="2"/>
+      <c r="W50" s="2"/>
+      <c r="X50" s="2"/>
+      <c r="Y50" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="Z50" s="2"/>
+      <c r="AA50" s="2"/>
+      <c r="AB50" s="2"/>
+      <c r="AC50" s="2"/>
+      <c r="AD50" s="2"/>
+      <c r="AE50" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="AF50" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="AG50" s="2"/>
+      <c r="AH50" s="2"/>
+      <c r="AI50" s="2"/>
+      <c r="AJ50" s="4">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="51" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K51" s="2"/>
+      <c r="L51" s="2"/>
+      <c r="M51" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N51" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="O51" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="P51" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q51" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R51" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="S51" s="2">
+        <v>1</v>
+      </c>
+      <c r="T51" s="2"/>
+      <c r="U51" s="2"/>
+      <c r="V51" s="2"/>
+      <c r="W51" s="2"/>
+      <c r="X51" s="2"/>
+      <c r="Y51" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="Z51" s="2"/>
+      <c r="AA51" s="2"/>
+      <c r="AB51" s="2"/>
+      <c r="AC51" s="2"/>
+      <c r="AD51" s="2"/>
+      <c r="AE51" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="AF51" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="AG51" s="2"/>
+      <c r="AH51" s="2"/>
+      <c r="AI51" s="2"/>
+      <c r="AJ51" s="4">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="52" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K52" s="2"/>
+      <c r="L52" s="2"/>
+      <c r="M52" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N52" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="O52" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="P52" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q52" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R52" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="S52" s="2">
+        <v>1</v>
+      </c>
+      <c r="T52" s="2"/>
+      <c r="U52" s="2"/>
+      <c r="V52" s="2"/>
+      <c r="W52" s="2"/>
+      <c r="X52" s="2"/>
+      <c r="Y52" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="Z52" s="2"/>
+      <c r="AA52" s="2"/>
+      <c r="AB52" s="2"/>
+      <c r="AC52" s="2"/>
+      <c r="AD52" s="2"/>
+      <c r="AE52" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="AF52" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="AG52" s="2"/>
+      <c r="AH52" s="2"/>
+      <c r="AI52" s="2"/>
+      <c r="AJ52" s="4">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="53" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J53" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K53" s="2"/>
+      <c r="L53" s="2"/>
+      <c r="M53" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N53" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="O53" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="P53" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q53" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R53" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="S53" s="2">
+        <v>1</v>
+      </c>
+      <c r="T53" s="2"/>
+      <c r="U53" s="2"/>
+      <c r="V53" s="2"/>
+      <c r="W53" s="2"/>
+      <c r="X53" s="2"/>
+      <c r="Y53" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="Z53" s="2"/>
+      <c r="AA53" s="2"/>
+      <c r="AB53" s="2"/>
+      <c r="AC53" s="2"/>
+      <c r="AD53" s="2"/>
+      <c r="AE53" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="AF53" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="AG53" s="2"/>
+      <c r="AH53" s="2"/>
+      <c r="AI53" s="2"/>
+      <c r="AJ53" s="4">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="54" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K54" s="2"/>
+      <c r="L54" s="2"/>
+      <c r="M54" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N54" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="O54" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="P54" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q54" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R54" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="S54" s="2">
+        <v>1</v>
+      </c>
+      <c r="T54" s="2"/>
+      <c r="U54" s="2"/>
+      <c r="V54" s="2"/>
+      <c r="W54" s="2"/>
+      <c r="X54" s="2"/>
+      <c r="Y54" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="Z54" s="2"/>
+      <c r="AA54" s="2"/>
+      <c r="AB54" s="2"/>
+      <c r="AC54" s="2"/>
+      <c r="AD54" s="2"/>
+      <c r="AE54" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="AF54" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="AG54" s="2"/>
+      <c r="AH54" s="2"/>
+      <c r="AI54" s="2"/>
+      <c r="AJ54" s="4">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="55" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K55" s="2"/>
+      <c r="L55" s="2"/>
+      <c r="M55" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N55" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="O55" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="P55" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q55" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R55" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="S55" s="2">
+        <v>1</v>
+      </c>
+      <c r="T55" s="2"/>
+      <c r="U55" s="2"/>
+      <c r="V55" s="2"/>
+      <c r="W55" s="2"/>
+      <c r="X55" s="2"/>
+      <c r="Y55" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="Z55" s="2"/>
+      <c r="AA55" s="2"/>
+      <c r="AB55" s="2"/>
+      <c r="AC55" s="2"/>
+      <c r="AD55" s="2"/>
+      <c r="AE55" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="AF55" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="AG55" s="2"/>
+      <c r="AH55" s="2"/>
+      <c r="AI55" s="2"/>
+      <c r="AJ55" s="4">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="56" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="J56" s="2"/>
+      <c r="K56" s="2"/>
+      <c r="L56" s="2"/>
+      <c r="M56" s="2"/>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+      <c r="P56" s="2"/>
+      <c r="Q56" s="2"/>
+      <c r="R56" s="2"/>
+      <c r="S56" s="2"/>
+      <c r="T56" s="2"/>
+      <c r="U56" s="2"/>
+      <c r="V56" s="2"/>
+      <c r="W56" s="2"/>
+      <c r="X56" s="2"/>
+      <c r="Y56" s="2"/>
+      <c r="Z56" s="2"/>
+      <c r="AA56" s="2"/>
+      <c r="AB56" s="2"/>
+      <c r="AC56" s="2"/>
+      <c r="AD56" s="2"/>
+      <c r="AE56" s="2"/>
+      <c r="AF56" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="AG56" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="AH56" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="AI56" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="AJ56" s="4">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="57" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="J57" s="2"/>
+      <c r="K57" s="2"/>
+      <c r="L57" s="2"/>
+      <c r="M57" s="2"/>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
+      <c r="P57" s="2"/>
+      <c r="Q57" s="2"/>
+      <c r="R57" s="2"/>
+      <c r="S57" s="2"/>
+      <c r="T57" s="2"/>
+      <c r="U57" s="2"/>
+      <c r="V57" s="2"/>
+      <c r="W57" s="2"/>
+      <c r="X57" s="2"/>
+      <c r="Y57" s="2"/>
+      <c r="Z57" s="2"/>
+      <c r="AA57" s="2"/>
+      <c r="AB57" s="2"/>
+      <c r="AC57" s="2"/>
+      <c r="AD57" s="2"/>
+      <c r="AE57" s="2"/>
+      <c r="AF57" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="AG57" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="AH57" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="AI57" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="AJ57" s="4">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="58" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="J58" s="2"/>
+      <c r="K58" s="2"/>
+      <c r="L58" s="2"/>
+      <c r="M58" s="2"/>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+      <c r="P58" s="2"/>
+      <c r="Q58" s="2"/>
+      <c r="R58" s="2"/>
+      <c r="S58" s="2"/>
+      <c r="T58" s="2"/>
+      <c r="U58" s="2"/>
+      <c r="V58" s="2"/>
+      <c r="W58" s="2"/>
+      <c r="X58" s="2"/>
+      <c r="Y58" s="2"/>
+      <c r="Z58" s="2"/>
+      <c r="AA58" s="2"/>
+      <c r="AB58" s="2"/>
+      <c r="AC58" s="2"/>
+      <c r="AD58" s="2"/>
+      <c r="AE58" s="2"/>
+      <c r="AF58" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="AG58" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="AH58" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="AI58" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="AJ58" s="4">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="59" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>268</v>
+      </c>
+      <c r="B59" t="s">
+        <v>269</v>
+      </c>
+      <c r="C59" t="s">
+        <v>276</v>
+      </c>
+      <c r="AJ59" s="4">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="60" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>270</v>
+      </c>
+      <c r="B60" t="s">
+        <v>271</v>
+      </c>
+      <c r="C60" t="s">
+        <v>277</v>
+      </c>
+      <c r="AJ60" s="4">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="61" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>272</v>
+      </c>
+      <c r="B61" t="s">
+        <v>273</v>
+      </c>
+      <c r="C61" t="s">
+        <v>278</v>
+      </c>
+      <c r="AJ61" s="4">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="62" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>274</v>
+      </c>
+      <c r="B62" t="s">
+        <v>275</v>
+      </c>
+      <c r="C62" t="s">
+        <v>279</v>
+      </c>
+      <c r="AJ62" s="4">
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/source/connector_service.xlsx
+++ b/source/connector_service.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\enterprise\omega\Папки отделов\Департамент закупівель та логістики\Відділ реінжинірингу процесів закупівель\Master data\З'єднувач\обработка\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93B275C0-E37B-4F3E-AD56-22F5686E962F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE685C71-D5F2-4526-8F10-3A83FA5DCE16}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11625" xr2:uid="{CE2CFF51-9F38-4EC7-9E81-657A284ABED4}"/>
   </bookViews>
   <sheets>
     <sheet name="Аркуш1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" concurrentManualCount="10"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="976" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="282">
   <si>
     <t>Номер карточки</t>
   </si>
@@ -1387,6 +1387,12 @@
   </si>
   <si>
     <t>Наконечник шланга підкачки (гайка-баранчик) штуцер 12мм (RIDER)</t>
+  </si>
+  <si>
+    <t>_1572209</t>
+  </si>
+  <si>
+    <t>_315019031</t>
   </si>
 </sst>
 </file>
@@ -1773,8 +1779,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3118E0D-448D-4EEB-9348-1247B3113B2C}">
-  <dimension ref="A1:AJ62"/>
+  <dimension ref="A1:AJ59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:36" ht="105" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -2648,26 +2657,26 @@
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>66</v>
+        <v>280</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>67</v>
+        <v>281</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>36</v>
@@ -2675,8 +2684,12 @@
       <c r="J12" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
+      <c r="K12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="M12" s="2" t="s">
         <v>40</v>
       </c>
@@ -2698,21 +2711,11 @@
       <c r="S12" s="2">
         <v>1.5</v>
       </c>
-      <c r="T12" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="U12" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="V12" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="W12" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="X12" s="2" t="s">
-        <v>75</v>
-      </c>
+      <c r="T12" s="2"/>
+      <c r="U12" s="2"/>
+      <c r="V12" s="2"/>
+      <c r="W12" s="2"/>
+      <c r="X12" s="2"/>
       <c r="Y12" s="2"/>
       <c r="Z12" s="2"/>
       <c r="AA12" s="2"/>
@@ -2725,24 +2728,24 @@
       <c r="AH12" s="2"/>
       <c r="AI12" s="2"/>
       <c r="AJ12">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2" t="s">
@@ -2763,10 +2766,10 @@
         <v>40</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>42</v>
@@ -2775,7 +2778,7 @@
         <v>43</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="S13" s="2">
         <v>1.5</v>
@@ -2812,23 +2815,21 @@
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>86</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="F14" s="2"/>
       <c r="G14" s="2" t="s">
         <v>70</v>
       </c>
@@ -2838,17 +2839,19 @@
       <c r="I14" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="J14" s="2"/>
+      <c r="J14" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>42</v>
@@ -2857,7 +2860,7 @@
         <v>43</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="S14" s="2">
         <v>1.5</v>
@@ -2874,7 +2877,9 @@
       <c r="W14" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="X14" s="2"/>
+      <c r="X14" s="2" t="s">
+        <v>75</v>
+      </c>
       <c r="Y14" s="2"/>
       <c r="Z14" s="2"/>
       <c r="AA14" s="2"/>
@@ -2892,19 +2897,19 @@
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>86</v>
@@ -2925,10 +2930,10 @@
         <v>40</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>42</v>
@@ -2937,7 +2942,7 @@
         <v>43</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="S15" s="2">
         <v>1.5</v>
@@ -2972,19 +2977,19 @@
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>86</v>
@@ -3034,9 +3039,7 @@
       <c r="W16" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="X16" s="2" t="s">
-        <v>75</v>
-      </c>
+      <c r="X16" s="2"/>
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
       <c r="AA16" s="2"/>
@@ -3054,19 +3057,19 @@
     </row>
     <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>86</v>
@@ -3087,10 +3090,10 @@
         <v>40</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>42</v>
@@ -3099,7 +3102,7 @@
         <v>43</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="S17" s="2">
         <v>1.5</v>
@@ -3136,21 +3139,23 @@
     </row>
     <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F18" s="2"/>
+        <v>98</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>86</v>
+      </c>
       <c r="G18" s="2" t="s">
         <v>70</v>
       </c>
@@ -3160,9 +3165,7 @@
       <c r="I18" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="J18" s="2" t="s">
-        <v>37</v>
-      </c>
+      <c r="J18" s="2"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2" t="s">
@@ -3218,10 +3221,10 @@
     </row>
     <row r="19" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>68</v>
@@ -3300,26 +3303,26 @@
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>36</v>
@@ -3330,63 +3333,71 @@
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
       <c r="M20" s="2" t="s">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="O20" s="2"/>
-      <c r="P20" s="2"/>
-      <c r="Q20" s="2"/>
-      <c r="R20" s="2"/>
-      <c r="S20" s="2"/>
-      <c r="T20" s="2"/>
-      <c r="U20" s="2"/>
-      <c r="V20" s="2"/>
-      <c r="W20" s="2"/>
-      <c r="X20" s="2"/>
-      <c r="Y20" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="Z20" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="AA20" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="AB20" s="2">
-        <v>6</v>
-      </c>
-      <c r="AC20" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="AD20" s="2" t="s">
-        <v>114</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S20" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="T20" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U20" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="V20" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="W20" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="X20" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y20" s="2"/>
+      <c r="Z20" s="2"/>
+      <c r="AA20" s="2"/>
+      <c r="AB20" s="2"/>
+      <c r="AC20" s="2"/>
+      <c r="AD20" s="2"/>
       <c r="AE20" s="2"/>
       <c r="AF20" s="2"/>
       <c r="AG20" s="2"/>
       <c r="AH20" s="2"/>
       <c r="AI20" s="2"/>
       <c r="AJ20">
-        <v>75</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2" t="s">
@@ -3407,7 +3418,7 @@
         <v>109</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
@@ -3429,7 +3440,7 @@
         <v>55</v>
       </c>
       <c r="AB21" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AC21" s="2" t="s">
         <v>113</v>
@@ -3448,10 +3459,10 @@
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>117</v>
@@ -3522,19 +3533,19 @@
     </row>
     <row r="23" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2" t="s">
@@ -3547,7 +3558,7 @@
         <v>36</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
@@ -3555,7 +3566,7 @@
         <v>109</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
@@ -3577,7 +3588,7 @@
         <v>55</v>
       </c>
       <c r="AB23" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC23" s="2" t="s">
         <v>113</v>
@@ -3591,24 +3602,24 @@
       <c r="AH23" s="2"/>
       <c r="AI23" s="2"/>
       <c r="AJ23">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2" t="s">
@@ -3629,7 +3640,7 @@
         <v>109</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" s="2"/>
@@ -3651,7 +3662,7 @@
         <v>55</v>
       </c>
       <c r="AB24" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AC24" s="2" t="s">
         <v>113</v>
@@ -3670,19 +3681,19 @@
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2" t="s">
@@ -3703,7 +3714,7 @@
         <v>109</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" s="2"/>
@@ -3725,7 +3736,7 @@
         <v>55</v>
       </c>
       <c r="AB25" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC25" s="2" t="s">
         <v>113</v>
@@ -3744,19 +3755,19 @@
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>260</v>
+        <v>124</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>260</v>
+        <v>124</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>261</v>
+        <v>125</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2" t="s">
@@ -3769,7 +3780,7 @@
         <v>36</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>134</v>
+        <v>55</v>
       </c>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
@@ -3790,7 +3801,7 @@
       <c r="W26" s="2"/>
       <c r="X26" s="2"/>
       <c r="Y26" s="2" t="s">
-        <v>211</v>
+        <v>111</v>
       </c>
       <c r="Z26" s="2" t="s">
         <v>112</v>
@@ -3813,24 +3824,24 @@
       <c r="AH26" s="2"/>
       <c r="AI26" s="2"/>
       <c r="AJ26">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2" t="s">
@@ -3851,7 +3862,7 @@
         <v>109</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" s="2"/>
@@ -3873,7 +3884,7 @@
         <v>55</v>
       </c>
       <c r="AB27" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AC27" s="2" t="s">
         <v>113</v>
@@ -3892,19 +3903,19 @@
     </row>
     <row r="28" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2" t="s">
@@ -3925,7 +3936,7 @@
         <v>109</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" s="2"/>
@@ -3944,10 +3955,10 @@
         <v>112</v>
       </c>
       <c r="AA28" s="2" t="s">
-        <v>139</v>
+        <v>55</v>
       </c>
       <c r="AB28" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC28" s="2" t="s">
         <v>113</v>
@@ -3961,28 +3972,46 @@
       <c r="AH28" s="2"/>
       <c r="AI28" s="2"/>
       <c r="AJ28">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>268</v>
-      </c>
-      <c r="B29" t="s">
-        <v>269</v>
-      </c>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
+      <c r="A29" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>265</v>
+      </c>
       <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
+      <c r="G29" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>134</v>
+      </c>
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
-      <c r="M29" s="2"/>
-      <c r="N29" s="2"/>
+      <c r="M29" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>110</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" s="2"/>
       <c r="Q29" s="2"/>
@@ -3993,29 +4022,43 @@
       <c r="V29" s="2"/>
       <c r="W29" s="2"/>
       <c r="X29" s="2"/>
-      <c r="Y29" s="2"/>
-      <c r="Z29" s="2"/>
-      <c r="AA29" s="2"/>
-      <c r="AB29" s="2"/>
-      <c r="AC29" s="2"/>
-      <c r="AD29" s="2"/>
+      <c r="Y29" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="Z29" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="AA29" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="AB29" s="2">
+        <v>6</v>
+      </c>
+      <c r="AC29" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD29" s="2" t="s">
+        <v>114</v>
+      </c>
       <c r="AE29" s="2"/>
       <c r="AF29" s="2"/>
       <c r="AG29" s="2"/>
       <c r="AH29" s="2"/>
       <c r="AI29" s="2"/>
       <c r="AJ29">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B30" t="s">
-        <v>271</v>
-      </c>
-      <c r="C30" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="C30" t="s">
+        <v>276</v>
+      </c>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
@@ -4054,12 +4097,14 @@
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B31" t="s">
-        <v>273</v>
-      </c>
-      <c r="C31" s="2"/>
+        <v>271</v>
+      </c>
+      <c r="C31" t="s">
+        <v>277</v>
+      </c>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
@@ -4098,12 +4143,14 @@
     </row>
     <row r="32" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B32" t="s">
-        <v>275</v>
-      </c>
-      <c r="C32" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="C32" t="s">
+        <v>278</v>
+      </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
@@ -4141,42 +4188,26 @@
       </c>
     </row>
     <row r="33" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>267</v>
-      </c>
+      <c r="A33" t="s">
+        <v>274</v>
+      </c>
+      <c r="B33" t="s">
+        <v>275</v>
+      </c>
+      <c r="C33" t="s">
+        <v>279</v>
+      </c>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
       <c r="F33" s="2"/>
-      <c r="G33" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>134</v>
-      </c>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
       <c r="K33" s="2"/>
       <c r="L33" s="2"/>
-      <c r="M33" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="N33" s="2" t="s">
-        <v>119</v>
-      </c>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" s="2"/>
       <c r="Q33" s="2"/>
@@ -4187,126 +4218,110 @@
       <c r="V33" s="2"/>
       <c r="W33" s="2"/>
       <c r="X33" s="2"/>
-      <c r="Y33" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="Z33" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="AA33" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="AB33" s="2">
-        <v>8</v>
-      </c>
-      <c r="AC33" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="AD33" s="2" t="s">
-        <v>114</v>
-      </c>
+      <c r="Y33" s="2"/>
+      <c r="Z33" s="2"/>
+      <c r="AA33" s="2"/>
+      <c r="AB33" s="2"/>
+      <c r="AC33" s="2"/>
+      <c r="AD33" s="2"/>
       <c r="AE33" s="2"/>
       <c r="AF33" s="2"/>
       <c r="AG33" s="2"/>
       <c r="AH33" s="2"/>
       <c r="AI33" s="2"/>
       <c r="AJ33">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
-    <row r="34" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>145</v>
+        <v>266</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>145</v>
+        <v>266</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>146</v>
+        <v>267</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2" t="s">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>148</v>
+        <v>108</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>36</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>55</v>
+        <v>134</v>
       </c>
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
       <c r="M34" s="2" t="s">
-        <v>40</v>
+        <v>109</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="O34" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="P34" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q34" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="R34" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="S34" s="2">
-        <v>1</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="O34" s="2"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2"/>
+      <c r="R34" s="2"/>
+      <c r="S34" s="2"/>
       <c r="T34" s="2"/>
       <c r="U34" s="2"/>
       <c r="V34" s="2"/>
       <c r="W34" s="2"/>
       <c r="X34" s="2"/>
       <c r="Y34" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="Z34" s="2"/>
-      <c r="AA34" s="2"/>
-      <c r="AB34" s="2"/>
-      <c r="AC34" s="2"/>
-      <c r="AD34" s="2"/>
-      <c r="AE34" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="AF34" s="2" t="s">
-        <v>152</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="Z34" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="AA34" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="AB34" s="2">
+        <v>8</v>
+      </c>
+      <c r="AC34" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD34" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="AE34" s="2"/>
+      <c r="AF34" s="2"/>
       <c r="AG34" s="2"/>
       <c r="AH34" s="2"/>
       <c r="AI34" s="2"/>
-      <c r="AJ34" s="4">
-        <v>183</v>
+      <c r="AJ34">
+        <v>78</v>
       </c>
     </row>
     <row r="35" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2" t="s">
@@ -4361,7 +4376,7 @@
         <v>151</v>
       </c>
       <c r="AF35" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="AG35" s="2"/>
       <c r="AH35" s="2"/>
@@ -4372,19 +4387,19 @@
     </row>
     <row r="36" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2" t="s">
@@ -4405,10 +4420,10 @@
         <v>40</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="P36" s="2" t="s">
         <v>42</v>
@@ -4417,7 +4432,7 @@
         <v>43</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="S36" s="2">
         <v>1</v>
@@ -4439,7 +4454,7 @@
         <v>151</v>
       </c>
       <c r="AF36" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="AG36" s="2"/>
       <c r="AH36" s="2"/>
@@ -4450,19 +4465,19 @@
     </row>
     <row r="37" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2" t="s">
@@ -4517,7 +4532,7 @@
         <v>151</v>
       </c>
       <c r="AF37" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="AG37" s="2"/>
       <c r="AH37" s="2"/>
@@ -4528,19 +4543,19 @@
     </row>
     <row r="38" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2" t="s">
@@ -4561,10 +4576,10 @@
         <v>40</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="P38" s="2" t="s">
         <v>42</v>
@@ -4573,7 +4588,7 @@
         <v>43</v>
       </c>
       <c r="R38" s="2" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="S38" s="2">
         <v>1</v>
@@ -4595,7 +4610,7 @@
         <v>151</v>
       </c>
       <c r="AF38" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="AG38" s="2"/>
       <c r="AH38" s="2"/>
@@ -4606,19 +4621,19 @@
     </row>
     <row r="39" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2" t="s">
@@ -4673,7 +4688,7 @@
         <v>151</v>
       </c>
       <c r="AF39" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="AG39" s="2"/>
       <c r="AH39" s="2"/>
@@ -4684,19 +4699,19 @@
     </row>
     <row r="40" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2" t="s">
@@ -4717,10 +4732,10 @@
         <v>40</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="P40" s="2" t="s">
         <v>42</v>
@@ -4729,7 +4744,7 @@
         <v>43</v>
       </c>
       <c r="R40" s="2" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="S40" s="2">
         <v>1</v>
@@ -4740,7 +4755,7 @@
       <c r="W40" s="2"/>
       <c r="X40" s="2"/>
       <c r="Y40" s="2" t="s">
-        <v>182</v>
+        <v>111</v>
       </c>
       <c r="Z40" s="2"/>
       <c r="AA40" s="2"/>
@@ -4751,30 +4766,30 @@
         <v>151</v>
       </c>
       <c r="AF40" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="AG40" s="2"/>
       <c r="AH40" s="2"/>
       <c r="AI40" s="2"/>
       <c r="AJ40" s="4">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="41" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2" t="s">
@@ -4829,7 +4844,7 @@
         <v>151</v>
       </c>
       <c r="AF41" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="AG41" s="2"/>
       <c r="AH41" s="2"/>
@@ -4840,10 +4855,10 @@
     </row>
     <row r="42" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>185</v>
@@ -4918,19 +4933,19 @@
     </row>
     <row r="43" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2" t="s">
@@ -4951,10 +4966,10 @@
         <v>40</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="P43" s="2" t="s">
         <v>42</v>
@@ -4963,7 +4978,7 @@
         <v>43</v>
       </c>
       <c r="R43" s="2" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="S43" s="2">
         <v>1</v>
@@ -4985,7 +5000,7 @@
         <v>151</v>
       </c>
       <c r="AF43" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="AG43" s="2"/>
       <c r="AH43" s="2"/>
@@ -4996,19 +5011,19 @@
     </row>
     <row r="44" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2" t="s">
@@ -5063,7 +5078,7 @@
         <v>151</v>
       </c>
       <c r="AF44" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="AG44" s="2"/>
       <c r="AH44" s="2"/>
@@ -5074,10 +5089,10 @@
     </row>
     <row r="45" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>195</v>
@@ -5152,19 +5167,19 @@
     </row>
     <row r="46" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2" t="s">
@@ -5185,10 +5200,10 @@
         <v>40</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="P46" s="2" t="s">
         <v>42</v>
@@ -5197,7 +5212,7 @@
         <v>43</v>
       </c>
       <c r="R46" s="2" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="S46" s="2">
         <v>1</v>
@@ -5219,7 +5234,7 @@
         <v>151</v>
       </c>
       <c r="AF46" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="AG46" s="2"/>
       <c r="AH46" s="2"/>
@@ -5230,19 +5245,19 @@
     </row>
     <row r="47" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="2" t="s">
@@ -5297,7 +5312,7 @@
         <v>151</v>
       </c>
       <c r="AF47" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="AG47" s="2"/>
       <c r="AH47" s="2"/>
@@ -5308,19 +5323,19 @@
     </row>
     <row r="48" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2" t="s">
@@ -5341,10 +5356,10 @@
         <v>40</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="P48" s="2" t="s">
         <v>42</v>
@@ -5353,7 +5368,7 @@
         <v>43</v>
       </c>
       <c r="R48" s="2" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="S48" s="2">
         <v>1</v>
@@ -5364,7 +5379,7 @@
       <c r="W48" s="2"/>
       <c r="X48" s="2"/>
       <c r="Y48" s="2" t="s">
-        <v>211</v>
+        <v>182</v>
       </c>
       <c r="Z48" s="2"/>
       <c r="AA48" s="2"/>
@@ -5375,30 +5390,30 @@
         <v>151</v>
       </c>
       <c r="AF48" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="AG48" s="2"/>
       <c r="AH48" s="2"/>
       <c r="AI48" s="2"/>
       <c r="AJ48" s="4">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="49" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2" t="s">
@@ -5453,7 +5468,7 @@
         <v>151</v>
       </c>
       <c r="AF49" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="AG49" s="2"/>
       <c r="AH49" s="2"/>
@@ -5464,19 +5479,19 @@
     </row>
     <row r="50" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2" t="s">
@@ -5497,10 +5512,10 @@
         <v>40</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="P50" s="2" t="s">
         <v>42</v>
@@ -5509,7 +5524,7 @@
         <v>43</v>
       </c>
       <c r="R50" s="2" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="S50" s="2">
         <v>1</v>
@@ -5531,7 +5546,7 @@
         <v>151</v>
       </c>
       <c r="AF50" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="AG50" s="2"/>
       <c r="AH50" s="2"/>
@@ -5542,19 +5557,19 @@
     </row>
     <row r="51" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2" t="s">
@@ -5609,7 +5624,7 @@
         <v>151</v>
       </c>
       <c r="AF51" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="AG51" s="2"/>
       <c r="AH51" s="2"/>
@@ -5620,10 +5635,10 @@
     </row>
     <row r="52" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>222</v>
@@ -5698,19 +5713,19 @@
     </row>
     <row r="53" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2" t="s">
@@ -5731,10 +5746,10 @@
         <v>40</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="P53" s="2" t="s">
         <v>42</v>
@@ -5743,7 +5758,7 @@
         <v>43</v>
       </c>
       <c r="R53" s="2" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="S53" s="2">
         <v>1</v>
@@ -5765,7 +5780,7 @@
         <v>151</v>
       </c>
       <c r="AF53" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="AG53" s="2"/>
       <c r="AH53" s="2"/>
@@ -5776,19 +5791,19 @@
     </row>
     <row r="54" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="2" t="s">
@@ -5843,7 +5858,7 @@
         <v>151</v>
       </c>
       <c r="AF54" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="AG54" s="2"/>
       <c r="AH54" s="2"/>
@@ -5854,10 +5869,10 @@
     </row>
     <row r="55" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>232</v>
@@ -5932,83 +5947,97 @@
     </row>
     <row r="56" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="2" t="s">
-        <v>240</v>
+        <v>147</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>241</v>
+        <v>148</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="J56" s="2"/>
+        <v>36</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="K56" s="2"/>
       <c r="L56" s="2"/>
-      <c r="M56" s="2"/>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
-      <c r="P56" s="2"/>
-      <c r="Q56" s="2"/>
-      <c r="R56" s="2"/>
-      <c r="S56" s="2"/>
+      <c r="M56" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N56" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="O56" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="P56" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q56" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R56" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="S56" s="2">
+        <v>1</v>
+      </c>
       <c r="T56" s="2"/>
       <c r="U56" s="2"/>
       <c r="V56" s="2"/>
       <c r="W56" s="2"/>
       <c r="X56" s="2"/>
-      <c r="Y56" s="2"/>
+      <c r="Y56" s="2" t="s">
+        <v>211</v>
+      </c>
       <c r="Z56" s="2"/>
       <c r="AA56" s="2"/>
       <c r="AB56" s="2"/>
       <c r="AC56" s="2"/>
       <c r="AD56" s="2"/>
-      <c r="AE56" s="2"/>
+      <c r="AE56" s="2" t="s">
+        <v>151</v>
+      </c>
       <c r="AF56" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="AG56" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="AH56" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="AI56" s="2" t="s">
-        <v>244</v>
-      </c>
+      <c r="AG56" s="2"/>
+      <c r="AH56" s="2"/>
+      <c r="AI56" s="2"/>
       <c r="AJ56" s="4">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="57" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2" t="s">
@@ -6052,7 +6081,7 @@
         <v>243</v>
       </c>
       <c r="AI57" s="2" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="AJ57" s="4">
         <v>186</v>
@@ -6060,19 +6089,19 @@
     </row>
     <row r="58" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2" t="s">
@@ -6116,66 +6145,74 @@
         <v>243</v>
       </c>
       <c r="AI58" s="2" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="AJ58" s="4">
         <v>186</v>
       </c>
     </row>
-    <row r="59" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>268</v>
-      </c>
-      <c r="B59" t="s">
-        <v>269</v>
-      </c>
-      <c r="C59" t="s">
-        <v>276</v>
+    <row r="59" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="J59" s="2"/>
+      <c r="K59" s="2"/>
+      <c r="L59" s="2"/>
+      <c r="M59" s="2"/>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" s="2"/>
+      <c r="Q59" s="2"/>
+      <c r="R59" s="2"/>
+      <c r="S59" s="2"/>
+      <c r="T59" s="2"/>
+      <c r="U59" s="2"/>
+      <c r="V59" s="2"/>
+      <c r="W59" s="2"/>
+      <c r="X59" s="2"/>
+      <c r="Y59" s="2"/>
+      <c r="Z59" s="2"/>
+      <c r="AA59" s="2"/>
+      <c r="AB59" s="2"/>
+      <c r="AC59" s="2"/>
+      <c r="AD59" s="2"/>
+      <c r="AE59" s="2"/>
+      <c r="AF59" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="AG59" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="AH59" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="AI59" s="2" t="s">
+        <v>254</v>
       </c>
       <c r="AJ59" s="4">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="60" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>270</v>
-      </c>
-      <c r="B60" t="s">
-        <v>271</v>
-      </c>
-      <c r="C60" t="s">
-        <v>277</v>
-      </c>
-      <c r="AJ60" s="4">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="61" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>272</v>
-      </c>
-      <c r="B61" t="s">
-        <v>273</v>
-      </c>
-      <c r="C61" t="s">
-        <v>278</v>
-      </c>
-      <c r="AJ61" s="4">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="62" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>274</v>
-      </c>
-      <c r="B62" t="s">
-        <v>275</v>
-      </c>
-      <c r="C62" t="s">
-        <v>279</v>
-      </c>
-      <c r="AJ62" s="4">
-        <v>74</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>
